--- a/artfynd/A 8533-2026 artfynd.xlsx
+++ b/artfynd/A 8533-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119401206</v>
+        <v>132439704</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Dlr</t>
+          <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551804</v>
+        <v>551742</v>
       </c>
       <c r="R2" t="n">
-        <v>6710029</v>
+        <v>6710013</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,27 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Egil Borgne</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+          <t>Egil Borgne</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119401050</v>
+        <v>132439701</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,46 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Dlr</t>
+          <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551844</v>
+        <v>551781</v>
       </c>
       <c r="R3" t="n">
-        <v>6710053</v>
+        <v>6710024</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Egil Borgne</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+          <t>Egil Borgne</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119401215</v>
+        <v>119401050</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,42 +905,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Dlr</t>
+          <t>Kroktjärnen, Kroktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551804</v>
+        <v>551844</v>
       </c>
       <c r="R4" t="n">
-        <v>6710029</v>
+        <v>6710053</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska spån, häckningskriterier.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,15 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119401440</v>
+        <v>119401206</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,27 +1021,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kroktjärnen, Dlr</t>
@@ -1120,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,21 +1099,15 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Brandspår stubbe</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1163,15 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119403674</v>
+        <v>119401440</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,14 +1160,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Dlr</t>
+          <t>Kroktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551651</v>
+        <v>551804</v>
       </c>
       <c r="R6" t="n">
-        <v>6710111</v>
+        <v>6710029</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,12 +1209,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera brandstubbar</t>
+          <t>Brandspår stubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132439699</v>
+        <v>119403674</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,42 +1253,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trylämnet, Dlr</t>
+          <t>Kroktjärnen, Kroktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551806</v>
+        <v>551651</v>
       </c>
       <c r="R7" t="n">
-        <v>6710025</v>
+        <v>6710111</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,57 +1310,58 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I äldre asp</t>
+          <t>Flera brandstubbar</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132439713</v>
+        <v>132439694</v>
       </c>
       <c r="B8" t="n">
-        <v>79952</v>
+        <v>79992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551709</v>
+        <v>551491</v>
       </c>
       <c r="R8" t="n">
-        <v>6709971</v>
+        <v>6709868</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,32 +1465,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132439706</v>
+        <v>132439695</v>
       </c>
       <c r="B9" t="n">
-        <v>97995</v>
+        <v>79992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1543,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551741</v>
+        <v>551486</v>
       </c>
       <c r="R9" t="n">
-        <v>6710013</v>
+        <v>6709869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132439712</v>
+        <v>132439697</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>79992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,39 +1583,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551743</v>
+        <v>551708</v>
       </c>
       <c r="R10" t="n">
-        <v>6710008</v>
+        <v>6709961</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132439697</v>
+        <v>132439698</v>
       </c>
       <c r="B11" t="n">
-        <v>79952</v>
+        <v>79992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551708</v>
+        <v>551710</v>
       </c>
       <c r="R11" t="n">
-        <v>6709961</v>
+        <v>6710002</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132439705</v>
+        <v>132439702</v>
       </c>
       <c r="B12" t="n">
-        <v>58119</v>
+        <v>79992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,39 +1797,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551745</v>
+        <v>551766</v>
       </c>
       <c r="R12" t="n">
-        <v>6710001</v>
+        <v>6710023</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1856,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1866,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,32 +1893,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132439715</v>
+        <v>132439713</v>
       </c>
       <c r="B13" t="n">
-        <v>97995</v>
+        <v>79992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1981,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551667</v>
+        <v>551709</v>
       </c>
       <c r="R13" t="n">
-        <v>6709965</v>
+        <v>6709971</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,50 +2000,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132439714</v>
+        <v>132439717</v>
       </c>
       <c r="B14" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551707</v>
+        <v>551531</v>
       </c>
       <c r="R14" t="n">
-        <v>6709970</v>
+        <v>6709855</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2070,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2080,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,48 +2107,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132439698</v>
+        <v>119401215</v>
       </c>
       <c r="B15" t="n">
-        <v>79952</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Trylämnet, Dlr</t>
+          <t>Kroktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551710</v>
+        <v>551804</v>
       </c>
       <c r="R15" t="n">
-        <v>6710002</v>
+        <v>6710029</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2230,22 +2180,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska spån, häckningskriterier.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,22 +2215,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132439716</v>
+        <v>132439699</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,27 +2238,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2312,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551553</v>
+        <v>551806</v>
       </c>
       <c r="R16" t="n">
-        <v>6709887</v>
+        <v>6710025</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,7 +2312,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I äldre asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,45 +2344,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132439704</v>
+        <v>132439710</v>
       </c>
       <c r="B17" t="n">
-        <v>92301</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1506</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551742</v>
+        <v>551739</v>
       </c>
       <c r="R17" t="n">
-        <v>6710013</v>
+        <v>6710004</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2419,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,12 +2429,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>Pågående bobygge i äldre asp, färska spån på marken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,14 +2461,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132439710</v>
+        <v>132439712</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2527,7 +2492,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2536,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551739</v>
+        <v>551743</v>
       </c>
       <c r="R18" t="n">
-        <v>6710004</v>
+        <v>6710008</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,7 +2536,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,12 +2546,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Pågående bobygge i äldre asp, färska spån på marken</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,10 +2573,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132439702</v>
+        <v>132439705</v>
       </c>
       <c r="B19" t="n">
-        <v>79952</v>
+        <v>58136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,34 +2584,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551766</v>
+        <v>551745</v>
       </c>
       <c r="R19" t="n">
-        <v>6710023</v>
+        <v>6710001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2693,7 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,45 +2685,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132439717</v>
+        <v>132439714</v>
       </c>
       <c r="B20" t="n">
-        <v>79952</v>
+        <v>8460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551531</v>
+        <v>551707</v>
       </c>
       <c r="R20" t="n">
-        <v>6709855</v>
+        <v>6709970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,6 +2794,332 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132439716</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>551553</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6709887</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132439706</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>551741</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6710013</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132439715</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>551667</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6709965</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8533-2026 artfynd.xlsx
+++ b/artfynd/A 8533-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439704</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439701</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119401050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119401206</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119401440</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119403674</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439694</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439695</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439697</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439698</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1890,6 +1945,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439702</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439713</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2104,6 +2169,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439717</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2224,6 +2294,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119401215</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2341,6 +2416,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439699</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2458,6 +2538,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439710</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2570,6 +2655,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439712</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2682,6 +2772,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439705</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2794,6 +2889,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439714</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2906,6 +3006,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439716</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3013,6 +3118,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439706</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3120,8 +3230,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439715</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>